--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ANTLERLESS_ELK_GENERAL_SEASON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ANTLERLESS_ELK_GENERAL_SEASON.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -669,7 +675,8 @@
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -737,7 +744,8 @@
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -805,7 +813,8 @@
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -872,8 +881,13 @@
           <t>49.2</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -941,7 +955,8 @@
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -1009,7 +1024,8 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -1077,7 +1093,8 @@
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -1145,7 +1162,8 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
@@ -1212,8 +1230,13 @@
           <t>44.5</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -1280,8 +1303,13 @@
           <t>34.9</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -1348,8 +1376,13 @@
           <t>35.5</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -1416,8 +1449,13 @@
           <t>62.8</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -1484,8 +1522,13 @@
           <t>38.5</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -1553,7 +1596,8 @@
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -1620,8 +1664,13 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -1688,8 +1737,13 @@
           <t>48.9</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -1757,7 +1811,8 @@
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
@@ -1825,7 +1880,8 @@
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -1892,8 +1948,13 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -1960,8 +2021,13 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2028,8 +2094,13 @@
           <t>35.2</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -2097,7 +2168,8 @@
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2164,8 +2236,13 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2232,8 +2309,13 @@
           <t>71.1</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2300,8 +2382,13 @@
           <t>50</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -2368,8 +2455,13 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr">
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2436,8 +2528,13 @@
           <t>16.7</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -2504,8 +2601,13 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2573,7 +2675,8 @@
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2641,7 +2744,8 @@
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -2708,8 +2812,13 @@
           <t>63.6</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -2776,8 +2885,13 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -2845,7 +2959,8 @@
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -2913,7 +3028,8 @@
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -2981,7 +3097,8 @@
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -3048,8 +3165,13 @@
           <t>36.8</t>
         </is>
       </c>
-      <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -3116,8 +3238,13 @@
           <t>93.3</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -3184,8 +3311,13 @@
           <t>77.6</t>
         </is>
       </c>
-      <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3252,8 +3384,13 @@
           <t>39.1</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3320,8 +3457,13 @@
           <t>51.4</t>
         </is>
       </c>
-      <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr">
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -3388,8 +3530,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3456,8 +3603,13 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr">
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3524,8 +3676,13 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -3592,8 +3749,13 @@
           <t>21.7</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -3660,8 +3822,13 @@
           <t>24.4</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -3728,8 +3895,13 @@
           <t>47.1</t>
         </is>
       </c>
-      <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -3796,8 +3968,13 @@
           <t>69.1</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3865,7 +4042,8 @@
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3932,8 +4110,13 @@
           <t>31.6</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -4000,8 +4183,13 @@
           <t>6.3</t>
         </is>
       </c>
-      <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -4068,8 +4256,13 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -4136,8 +4329,13 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr">
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -4204,8 +4402,13 @@
           <t>47.4</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -4273,7 +4476,8 @@
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -4340,8 +4544,13 @@
           <t>8.3</t>
         </is>
       </c>
-      <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -4408,8 +4617,13 @@
           <t>13.8</t>
         </is>
       </c>
-      <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4477,7 +4691,8 @@
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -4544,8 +4759,13 @@
           <t>24.7</t>
         </is>
       </c>
-      <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -4612,8 +4832,13 @@
           <t>40</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -4680,8 +4905,13 @@
           <t>40</t>
         </is>
       </c>
-      <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -4749,7 +4979,8 @@
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -4817,7 +5048,8 @@
         </is>
       </c>
       <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -4884,8 +5116,13 @@
           <t>45.9</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -4952,8 +5189,13 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>14.5</t>
         </is>
@@ -5020,8 +5262,13 @@
           <t>26</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
@@ -5072,8 +5319,13 @@
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
-      <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr"/>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" s="6" t="inlineStr"/>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
@@ -5125,7 +5377,8 @@
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -5192,8 +5445,13 @@
           <t>42.3</t>
         </is>
       </c>
-      <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr">
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -5260,8 +5518,13 @@
           <t>37.9</t>
         </is>
       </c>
-      <c r="M72" s="4" t="inlineStr"/>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -5328,8 +5591,13 @@
           <t>57.6</t>
         </is>
       </c>
-      <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr">
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -5396,8 +5664,13 @@
           <t>78.1</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -5465,7 +5738,8 @@
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" s="6" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -5533,7 +5807,8 @@
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -5601,7 +5876,8 @@
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="6" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -5668,8 +5944,13 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="M78" s="4" t="inlineStr"/>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -5737,7 +6018,8 @@
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -5804,8 +6086,13 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -5872,8 +6159,13 @@
           <t>34.9</t>
         </is>
       </c>
-      <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="6" t="inlineStr">
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -5940,8 +6232,13 @@
           <t>47.7</t>
         </is>
       </c>
-      <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -6008,8 +6305,13 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="6" t="inlineStr">
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -6076,8 +6378,13 @@
           <t>40</t>
         </is>
       </c>
-      <c r="M84" s="4" t="inlineStr"/>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="M84" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -6144,8 +6451,13 @@
           <t>17.4</t>
         </is>
       </c>
-      <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="6" t="inlineStr">
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -6212,8 +6524,13 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="M86" s="4" t="inlineStr"/>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="M86" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -6280,8 +6597,13 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="6" t="inlineStr">
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -6348,8 +6670,13 @@
           <t>25</t>
         </is>
       </c>
-      <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr">
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -6417,7 +6744,8 @@
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr"/>
-      <c r="N89" s="6" t="inlineStr">
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" s="6" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
@@ -6468,8 +6796,13 @@
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr"/>
-      <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr"/>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -6533,7 +6866,8 @@
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr"/>
-      <c r="N91" s="6" t="inlineStr">
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" s="6" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -6601,7 +6935,8 @@
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr">
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -6669,7 +7004,8 @@
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="6" t="inlineStr">
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" s="6" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -6737,7 +7073,8 @@
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -6805,7 +7142,8 @@
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr"/>
-      <c r="N95" s="6" t="inlineStr">
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" s="6" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -6873,7 +7211,8 @@
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr"/>
-      <c r="N96" s="4" t="inlineStr">
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -6941,7 +7280,8 @@
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="6" t="inlineStr">
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -7008,8 +7348,13 @@
           <t>82.6</t>
         </is>
       </c>
-      <c r="M98" s="4" t="inlineStr"/>
-      <c r="N98" s="4" t="inlineStr">
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -7076,8 +7421,13 @@
           <t>5.3</t>
         </is>
       </c>
-      <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="6" t="inlineStr">
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -7145,7 +7495,8 @@
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -7212,8 +7563,13 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="M101" s="6" t="inlineStr"/>
-      <c r="N101" s="6" t="inlineStr">
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" s="6" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -7281,7 +7637,8 @@
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr">
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -7349,7 +7706,8 @@
         </is>
       </c>
       <c r="M103" s="6" t="inlineStr"/>
-      <c r="N103" s="6" t="inlineStr">
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" s="6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -7417,7 +7775,8 @@
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -7485,7 +7844,8 @@
         </is>
       </c>
       <c r="M105" s="6" t="inlineStr"/>
-      <c r="N105" s="6" t="inlineStr">
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -7549,7 +7909,8 @@
       </c>
       <c r="L106" s="4" t="inlineStr"/>
       <c r="M106" s="4" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr"/>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
@@ -7612,8 +7973,13 @@
           <t>10</t>
         </is>
       </c>
-      <c r="M107" s="6" t="inlineStr"/>
-      <c r="N107" s="6" t="inlineStr">
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -7680,8 +8046,13 @@
           <t>14.8</t>
         </is>
       </c>
-      <c r="M108" s="4" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -7748,8 +8119,13 @@
           <t>61.3</t>
         </is>
       </c>
-      <c r="M109" s="6" t="inlineStr"/>
-      <c r="N109" s="6" t="inlineStr">
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" s="6" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -7804,8 +8180,13 @@
           <t>60</t>
         </is>
       </c>
-      <c r="M110" s="4" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr">
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -7873,7 +8254,8 @@
         </is>
       </c>
       <c r="M111" s="6" t="inlineStr"/>
-      <c r="N111" s="6" t="inlineStr">
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -7941,7 +8323,8 @@
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" s="4" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -8008,8 +8391,13 @@
           <t>91.4</t>
         </is>
       </c>
-      <c r="M113" s="6" t="inlineStr"/>
-      <c r="N113" s="6" t="inlineStr">
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -8076,8 +8464,13 @@
           <t>17.8</t>
         </is>
       </c>
-      <c r="M114" s="4" t="inlineStr"/>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" s="4" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -8144,8 +8537,13 @@
           <t>13.4</t>
         </is>
       </c>
-      <c r="M115" s="6" t="inlineStr"/>
-      <c r="N115" s="6" t="inlineStr">
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
